--- a/DIESEL SERFOCOL- V01.xlsx
+++ b/DIESEL SERFOCOL- V01.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\Serfocol\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\STREAMLIT WEB\SERFOCOL PROGRAMACION PY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{256AE1A5-F335-4BEB-8ECD-33B1437B3CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA3CCEF-F1EE-46A9-A797-CC11C5B17A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DIESEL SERFOCOL" sheetId="1" r:id="rId1"/>
     <sheet name="RESUMEN" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DIESEL SERFOCOL'!$A$9:$F$279</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DIESEL SERFOCOL'!$A$9:$F$281</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="39">
   <si>
     <t>Planta</t>
   </si>
@@ -3488,8 +3488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:F1000"/>
+  <dimension ref="A1:F1002"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.6328125" customWidth="1"/>
@@ -3527,8 +3526,8 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <f>+F280</f>
-        <v>1513</v>
+        <f>+F282</f>
+        <v>13992</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -3567,7 +3566,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>45027</v>
       </c>
@@ -3587,7 +3586,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>45028</v>
       </c>
@@ -3607,7 +3606,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>45031</v>
       </c>
@@ -3627,7 +3626,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>45034</v>
       </c>
@@ -3647,7 +3646,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>45036</v>
       </c>
@@ -3667,7 +3666,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>45041</v>
       </c>
@@ -3687,7 +3686,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>45042</v>
       </c>
@@ -3707,7 +3706,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>45044</v>
       </c>
@@ -3727,7 +3726,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
         <v>45049</v>
       </c>
@@ -3747,7 +3746,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>45054</v>
       </c>
@@ -3767,7 +3766,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
         <v>45055</v>
       </c>
@@ -3787,7 +3786,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
         <v>45058</v>
       </c>
@@ -3807,7 +3806,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
         <v>45061</v>
       </c>
@@ -3827,7 +3826,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
         <v>45064</v>
       </c>
@@ -3847,7 +3846,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
         <v>45065</v>
       </c>
@@ -3867,7 +3866,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
         <v>45070</v>
       </c>
@@ -3887,7 +3886,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
         <v>45075</v>
       </c>
@@ -3907,7 +3906,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>45079</v>
       </c>
@@ -3927,7 +3926,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
         <v>45083</v>
       </c>
@@ -3947,7 +3946,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
         <v>45086</v>
       </c>
@@ -3967,7 +3966,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
         <v>45090</v>
       </c>
@@ -3987,7 +3986,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
         <v>45093</v>
       </c>
@@ -4007,7 +4006,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
         <v>45098</v>
       </c>
@@ -4027,7 +4026,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>45104</v>
       </c>
@@ -4047,7 +4046,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4">
         <v>45106</v>
       </c>
@@ -4067,7 +4066,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4">
         <v>45111</v>
       </c>
@@ -4087,7 +4086,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4">
         <v>45118</v>
       </c>
@@ -4107,7 +4106,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="4">
         <v>45121</v>
       </c>
@@ -4127,7 +4126,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="4">
         <v>45121</v>
       </c>
@@ -4147,7 +4146,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
         <v>45124</v>
       </c>
@@ -4167,7 +4166,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="4">
         <v>45128</v>
       </c>
@@ -4187,7 +4186,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
         <v>45131</v>
       </c>
@@ -4207,7 +4206,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="4">
         <v>45133</v>
       </c>
@@ -4227,7 +4226,7 @@
         <v>53.5</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4">
         <v>45136</v>
       </c>
@@ -4247,7 +4246,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4">
         <v>45139</v>
       </c>
@@ -4267,7 +4266,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4">
         <v>45141</v>
       </c>
@@ -4287,7 +4286,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4">
         <v>45143</v>
       </c>
@@ -4307,7 +4306,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4">
         <v>45146</v>
       </c>
@@ -4327,7 +4326,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4">
         <v>45149</v>
       </c>
@@ -4347,7 +4346,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
         <v>45153</v>
       </c>
@@ -4367,7 +4366,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4">
         <v>45156</v>
       </c>
@@ -4387,7 +4386,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
         <v>45160</v>
       </c>
@@ -4407,7 +4406,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4">
         <v>45161</v>
       </c>
@@ -4427,7 +4426,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4">
         <v>45166</v>
       </c>
@@ -4447,7 +4446,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4">
         <v>45168</v>
       </c>
@@ -4467,7 +4466,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4">
         <v>45170</v>
       </c>
@@ -4487,7 +4486,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4">
         <v>45173</v>
       </c>
@@ -4507,7 +4506,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4">
         <v>45177</v>
       </c>
@@ -4527,7 +4526,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4">
         <v>45181</v>
       </c>
@@ -4547,7 +4546,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4">
         <v>45184</v>
       </c>
@@ -4567,7 +4566,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4">
         <v>45185</v>
       </c>
@@ -4587,7 +4586,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4">
         <v>45190</v>
       </c>
@@ -4607,7 +4606,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4">
         <v>45194</v>
       </c>
@@ -4627,7 +4626,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4">
         <v>45197</v>
       </c>
@@ -4647,7 +4646,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4">
         <v>45202</v>
       </c>
@@ -4667,7 +4666,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4">
         <v>45204</v>
       </c>
@@ -4687,7 +4686,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4">
         <v>45210</v>
       </c>
@@ -4707,7 +4706,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4">
         <v>45213</v>
       </c>
@@ -4727,7 +4726,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4">
         <v>45217</v>
       </c>
@@ -4747,7 +4746,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4">
         <v>45224</v>
       </c>
@@ -4767,7 +4766,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4">
         <v>45229</v>
       </c>
@@ -4787,7 +4786,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4">
         <v>45236</v>
       </c>
@@ -4807,7 +4806,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4">
         <v>45240</v>
       </c>
@@ -4827,7 +4826,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4">
         <v>45246</v>
       </c>
@@ -4847,7 +4846,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4">
         <v>45250</v>
       </c>
@@ -4867,7 +4866,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4">
         <v>45254</v>
       </c>
@@ -4887,7 +4886,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4">
         <v>45259</v>
       </c>
@@ -4907,7 +4906,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4">
         <v>45265</v>
       </c>
@@ -4927,7 +4926,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4">
         <v>45271</v>
       </c>
@@ -4947,7 +4946,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4">
         <v>45275</v>
       </c>
@@ -4967,7 +4966,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4">
         <v>45280</v>
       </c>
@@ -4987,7 +4986,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4">
         <v>45286</v>
       </c>
@@ -5007,7 +5006,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4">
         <v>45294</v>
       </c>
@@ -5027,7 +5026,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4">
         <v>45299</v>
       </c>
@@ -5047,7 +5046,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4">
         <v>45302</v>
       </c>
@@ -5067,7 +5066,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4">
         <v>45307</v>
       </c>
@@ -5087,7 +5086,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4">
         <v>45310</v>
       </c>
@@ -5107,7 +5106,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4">
         <v>45316</v>
       </c>
@@ -5127,7 +5126,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4">
         <v>45322</v>
       </c>
@@ -5147,7 +5146,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4">
         <v>45327</v>
       </c>
@@ -5167,7 +5166,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4">
         <v>45331</v>
       </c>
@@ -5187,7 +5186,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4">
         <v>45336</v>
       </c>
@@ -5207,7 +5206,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4">
         <v>45339</v>
       </c>
@@ -5227,7 +5226,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4">
         <v>45342</v>
       </c>
@@ -5247,7 +5246,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="4">
         <v>45349</v>
       </c>
@@ -5267,7 +5266,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4">
         <v>45355</v>
       </c>
@@ -5287,7 +5286,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4">
         <v>45358</v>
       </c>
@@ -5307,7 +5306,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4">
         <v>45366</v>
       </c>
@@ -5327,7 +5326,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="4">
         <v>45370</v>
       </c>
@@ -5347,7 +5346,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="99" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4">
         <v>45376</v>
       </c>
@@ -5367,7 +5366,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="100" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="4">
         <v>45383</v>
       </c>
@@ -5387,7 +5386,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4">
         <v>45385</v>
       </c>
@@ -5407,7 +5406,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="4">
         <v>45390</v>
       </c>
@@ -5427,7 +5426,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="4">
         <v>45394</v>
       </c>
@@ -5447,7 +5446,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="4">
         <v>45399</v>
       </c>
@@ -5467,7 +5466,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="4">
         <v>45402</v>
       </c>
@@ -5487,7 +5486,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="4">
         <v>45415</v>
       </c>
@@ -5507,7 +5506,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="4">
         <v>45420</v>
       </c>
@@ -5527,7 +5526,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="4">
         <v>45428</v>
       </c>
@@ -5547,7 +5546,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="109" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="4">
         <v>45432</v>
       </c>
@@ -5567,7 +5566,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="4">
         <v>45436</v>
       </c>
@@ -5587,7 +5586,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="4">
         <v>45441</v>
       </c>
@@ -5607,7 +5606,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="112" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="4">
         <v>45444</v>
       </c>
@@ -5627,7 +5626,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="113" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="4">
         <v>45449</v>
       </c>
@@ -5647,7 +5646,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="114" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="4">
         <v>45455</v>
       </c>
@@ -5667,7 +5666,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="4">
         <v>45458</v>
       </c>
@@ -5687,7 +5686,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="4">
         <v>45462</v>
       </c>
@@ -5707,7 +5706,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="117" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="4">
         <v>45467</v>
       </c>
@@ -5727,7 +5726,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="118" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="4">
         <v>45471</v>
       </c>
@@ -5747,7 +5746,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="4">
         <v>45475</v>
       </c>
@@ -5767,7 +5766,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="4">
         <v>45478</v>
       </c>
@@ -5787,7 +5786,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="4">
         <v>45482</v>
       </c>
@@ -5807,7 +5806,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="4">
         <v>45486</v>
       </c>
@@ -5827,7 +5826,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="123" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="4">
         <v>45492</v>
       </c>
@@ -5847,7 +5846,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="4">
         <v>45497</v>
       </c>
@@ -5867,7 +5866,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="125" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="4">
         <v>45499</v>
       </c>
@@ -5887,7 +5886,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="126" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="4">
         <v>45504</v>
       </c>
@@ -5907,7 +5906,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="127" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="4">
         <v>45510</v>
       </c>
@@ -5927,7 +5926,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="128" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="4">
         <v>45514</v>
       </c>
@@ -5947,7 +5946,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="4">
         <v>45520</v>
       </c>
@@ -5967,7 +5966,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="4">
         <v>45530</v>
       </c>
@@ -5987,7 +5986,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="131" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="4">
         <v>45533</v>
       </c>
@@ -6007,7 +6006,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="132" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="4">
         <v>45538</v>
       </c>
@@ -6027,7 +6026,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="133" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="4">
         <v>45540</v>
       </c>
@@ -6047,7 +6046,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="4">
         <v>45546</v>
       </c>
@@ -6067,7 +6066,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="135" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="4">
         <v>45551</v>
       </c>
@@ -6087,7 +6086,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="136" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="4">
         <v>45560</v>
       </c>
@@ -6107,7 +6106,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="137" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="4">
         <v>45565</v>
       </c>
@@ -6127,7 +6126,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="4">
         <v>45570</v>
       </c>
@@ -6147,7 +6146,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="139" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="4">
         <v>45573</v>
       </c>
@@ -6167,7 +6166,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="140" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="4">
         <v>45577</v>
       </c>
@@ -6187,7 +6186,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="141" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="4">
         <v>45581</v>
       </c>
@@ -6207,7 +6206,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="142" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="4">
         <v>45586</v>
       </c>
@@ -6227,7 +6226,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="4">
         <v>45591</v>
       </c>
@@ -6247,7 +6246,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="144" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="4">
         <v>45596</v>
       </c>
@@ -6267,7 +6266,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="145" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="4">
         <v>45602</v>
       </c>
@@ -6287,7 +6286,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="146" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="4">
         <v>45608</v>
       </c>
@@ -6307,7 +6306,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="4">
         <v>45612</v>
       </c>
@@ -6327,7 +6326,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="4">
         <v>45616</v>
       </c>
@@ -6347,7 +6346,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="4">
         <v>45621</v>
       </c>
@@ -6367,7 +6366,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="4">
         <v>45624</v>
       </c>
@@ -6387,7 +6386,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="151" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="4">
         <v>45630</v>
       </c>
@@ -6407,7 +6406,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="152" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="4">
         <v>45633</v>
       </c>
@@ -6427,7 +6426,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="153" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="4">
         <v>45636</v>
       </c>
@@ -6447,7 +6446,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="4">
         <v>45642</v>
       </c>
@@ -6467,7 +6466,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="155" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="4">
         <v>45646</v>
       </c>
@@ -6487,7 +6486,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="156" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="4">
         <v>45650</v>
       </c>
@@ -6507,7 +6506,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="4">
         <v>45656</v>
       </c>
@@ -6527,7 +6526,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="4">
         <v>45661</v>
       </c>
@@ -6547,7 +6546,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="159" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="4">
         <v>45665</v>
       </c>
@@ -6567,7 +6566,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="160" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="4">
         <v>45668</v>
       </c>
@@ -6587,7 +6586,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="161" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A161" s="4">
         <v>45671</v>
       </c>
@@ -6607,7 +6606,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="162" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A162" s="4">
         <v>45674</v>
       </c>
@@ -6627,7 +6626,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="163" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="4">
         <v>45677</v>
       </c>
@@ -6647,7 +6646,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="164" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="4">
         <v>45679</v>
       </c>
@@ -6667,7 +6666,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="165" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="4">
         <v>45681</v>
       </c>
@@ -6687,7 +6686,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="166" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="9">
         <v>45686</v>
       </c>
@@ -6707,7 +6706,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A167" s="4">
         <v>45689</v>
       </c>
@@ -6727,7 +6726,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="168" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="4">
         <v>45693</v>
       </c>
@@ -6747,7 +6746,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="169" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A169" s="4">
         <v>45695</v>
       </c>
@@ -6767,7 +6766,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="170" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="4">
         <v>45698</v>
       </c>
@@ -6787,7 +6786,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A171" s="4">
         <v>45701</v>
       </c>
@@ -6807,7 +6806,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="172" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A172" s="4">
         <v>45707</v>
       </c>
@@ -6827,7 +6826,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="173" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A173" s="4">
         <v>45710</v>
       </c>
@@ -6847,7 +6846,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="174" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="4">
         <v>45714</v>
       </c>
@@ -6867,7 +6866,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="175" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A175" s="4">
         <v>45717</v>
       </c>
@@ -6887,7 +6886,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="176" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="4">
         <v>45720</v>
       </c>
@@ -6907,7 +6906,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="4">
         <v>45723</v>
       </c>
@@ -6927,7 +6926,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="4">
         <v>45728</v>
       </c>
@@ -6947,7 +6946,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="4">
         <v>45731</v>
       </c>
@@ -6967,7 +6966,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="180" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="4">
         <v>45736</v>
       </c>
@@ -6987,7 +6986,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="181" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="4">
         <v>45741</v>
       </c>
@@ -7007,7 +7006,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="182" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="4">
         <v>45745</v>
       </c>
@@ -7027,7 +7026,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="183" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A183" s="4">
         <v>45750</v>
       </c>
@@ -7047,7 +7046,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="184" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A184" s="4">
         <v>45752</v>
       </c>
@@ -7067,7 +7066,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="4">
         <v>45756</v>
       </c>
@@ -7087,7 +7086,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="186" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="4">
         <v>45758</v>
       </c>
@@ -7107,7 +7106,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="187" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="4">
         <v>45763</v>
       </c>
@@ -7127,7 +7126,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="4">
         <v>45768</v>
       </c>
@@ -7147,7 +7146,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="189" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="4">
         <v>45775</v>
       </c>
@@ -7167,7 +7166,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="4">
         <v>45776</v>
       </c>
@@ -7187,7 +7186,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="4">
         <v>45781</v>
       </c>
@@ -7207,7 +7206,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="192" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A192" s="4">
         <v>45785</v>
       </c>
@@ -7227,7 +7226,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="193" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="4">
         <v>45789</v>
       </c>
@@ -7247,7 +7246,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="194" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A194" s="4">
         <v>45793</v>
       </c>
@@ -7267,7 +7266,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="195" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="4">
         <v>45799</v>
       </c>
@@ -7287,7 +7286,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A196" s="4">
         <v>45803</v>
       </c>
@@ -7307,7 +7306,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="197" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="4">
         <v>45805</v>
       </c>
@@ -7327,7 +7326,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="198" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A198" s="4">
         <v>45808</v>
       </c>
@@ -7347,7 +7346,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="199" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="4">
         <v>45812</v>
       </c>
@@ -7367,7 +7366,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="200" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="4">
         <v>45814</v>
       </c>
@@ -7387,7 +7386,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="201" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A201" s="4">
         <v>45818</v>
       </c>
@@ -7407,7 +7406,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="202" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A202" s="4">
         <v>45824</v>
       </c>
@@ -7427,7 +7426,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="203" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" s="4">
         <v>45827</v>
       </c>
@@ -7447,7 +7446,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="204" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A204" s="4">
         <v>45833</v>
       </c>
@@ -7467,7 +7466,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="205" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A205" s="4">
         <v>45838</v>
       </c>
@@ -7487,7 +7486,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="206" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="4">
         <v>45841</v>
       </c>
@@ -7507,7 +7506,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="207" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A207" s="4">
         <v>45845</v>
       </c>
@@ -7527,7 +7526,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="208" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="4">
         <v>45847</v>
       </c>
@@ -7547,7 +7546,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A209" s="4">
         <v>45848</v>
       </c>
@@ -7567,7 +7566,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="210" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A210" s="4">
         <v>45853</v>
       </c>
@@ -7587,7 +7586,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="211" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A211" s="4">
         <v>45857</v>
       </c>
@@ -7607,7 +7606,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="4">
         <v>45861</v>
       </c>
@@ -7627,7 +7626,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A213" s="4">
         <v>45866</v>
       </c>
@@ -7647,7 +7646,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="214" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A214" s="4">
         <v>45868</v>
       </c>
@@ -7667,7 +7666,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A215" s="4">
         <v>45871</v>
       </c>
@@ -7687,7 +7686,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="216" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A216" s="4">
         <v>45875</v>
       </c>
@@ -7707,7 +7706,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="217" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A217" s="4">
         <v>45877</v>
       </c>
@@ -7727,7 +7726,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A218" s="4">
         <v>45881</v>
       </c>
@@ -7747,7 +7746,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="219" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" s="4">
         <v>45883</v>
       </c>
@@ -7767,7 +7766,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="220" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" s="4">
         <v>45887</v>
       </c>
@@ -7787,7 +7786,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="221" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A221" s="4">
         <v>45889</v>
       </c>
@@ -7807,7 +7806,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="222" spans="1:6" s="16" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:6" s="16" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A222" s="4">
         <v>45891</v>
       </c>
@@ -7827,7 +7826,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="223" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A223" s="4">
         <v>45894</v>
       </c>
@@ -7847,7 +7846,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="224" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A224" s="4">
         <v>45896</v>
       </c>
@@ -7867,7 +7866,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="225" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" s="4">
         <v>45899</v>
       </c>
@@ -7887,7 +7886,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="226" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" s="4">
         <v>45902</v>
       </c>
@@ -7907,7 +7906,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="227" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" s="4">
         <v>45909</v>
       </c>
@@ -7927,7 +7926,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="228" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A228" s="14">
         <v>45920</v>
       </c>
@@ -7947,7 +7946,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="229" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A229" s="4">
         <v>45930</v>
       </c>
@@ -7967,7 +7966,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="230" spans="1:6" s="16" customFormat="1" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:6" s="16" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A230" s="4">
         <v>45933</v>
       </c>
@@ -7987,7 +7986,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="231" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" s="4">
         <v>45937</v>
       </c>
@@ -8007,7 +8006,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="232" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="4">
         <v>45939</v>
       </c>
@@ -8027,7 +8026,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="233" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A233" s="4">
         <v>45944</v>
       </c>
@@ -8047,7 +8046,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="234" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A234" s="4">
         <v>45947</v>
       </c>
@@ -8067,7 +8066,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="235" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="4">
         <v>45951</v>
       </c>
@@ -8087,7 +8086,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="236" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A236" s="14">
         <v>45952</v>
       </c>
@@ -8107,7 +8106,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="237" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="4">
         <v>45957</v>
       </c>
@@ -8127,7 +8126,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="238" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="4">
         <v>45960</v>
       </c>
@@ -8147,7 +8146,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="239" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="4">
         <v>45965</v>
       </c>
@@ -8167,7 +8166,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="240" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="4">
         <v>45979</v>
       </c>
@@ -8187,7 +8186,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="241" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="4">
         <v>45982</v>
       </c>
@@ -8207,7 +8206,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="242" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="4">
         <v>45987</v>
       </c>
@@ -8227,7 +8226,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="243" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A243" s="4">
         <v>45992</v>
       </c>
@@ -8247,7 +8246,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="244" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="4">
         <v>45995</v>
       </c>
@@ -8267,7 +8266,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="245" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A245" s="4">
         <v>46002</v>
       </c>
@@ -8287,7 +8286,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="246" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="4">
         <v>46007</v>
       </c>
@@ -8307,7 +8306,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="247" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="4">
         <v>46017</v>
       </c>
@@ -8327,7 +8326,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="248" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="4">
         <v>46022</v>
       </c>
@@ -8968,26 +8967,64 @@
       </c>
     </row>
     <row r="280" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A280" s="5"/>
-      <c r="B280" s="5"/>
-      <c r="C280" s="5"/>
-      <c r="D280" s="5"/>
-      <c r="E280" s="5"/>
-      <c r="F280" s="5">
-        <f>SUBTOTAL(109,(F10:F279))</f>
-        <v>1513</v>
+      <c r="A280" s="4">
+        <v>46176</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C280" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D280" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E280" s="5">
+        <v>1626</v>
+      </c>
+      <c r="F280" s="13">
+        <v>50</v>
       </c>
     </row>
     <row r="281" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A281" s="5"/>
-      <c r="B281" s="5"/>
-      <c r="C281" s="5"/>
-      <c r="D281" s="5"/>
-      <c r="E281" s="5"/>
-      <c r="F281" s="5"/>
-    </row>
-    <row r="282" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="283" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="A281" s="4">
+        <v>46179</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C281" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D281" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E281" s="5">
+        <v>1627</v>
+      </c>
+      <c r="F281" s="13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A282" s="5"/>
+      <c r="B282" s="5"/>
+      <c r="C282" s="5"/>
+      <c r="D282" s="5"/>
+      <c r="E282" s="5"/>
+      <c r="F282" s="5">
+        <f>SUBTOTAL(109,(F10:F281))</f>
+        <v>13992</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A283" s="5"/>
+      <c r="B283" s="5"/>
+      <c r="C283" s="5"/>
+      <c r="D283" s="5"/>
+      <c r="E283" s="5"/>
+      <c r="F283" s="5"/>
+    </row>
     <row r="284" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="285" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="286" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -9705,14 +9742,10 @@
     <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1001" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1002" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <autoFilter ref="A9:F279" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <dateGroupItem year="2026" dateTimeGrouping="year"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A9:F281" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:B4"/>
   </mergeCells>

--- a/DIESEL SERFOCOL- V01.xlsx
+++ b/DIESEL SERFOCOL- V01.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\STREAMLIT WEB\SERFOCOL PROGRAMACION PY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA3CCEF-F1EE-46A9-A797-CC11C5B17A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC184282-B31A-40F1-8532-836115384B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="39">
   <si>
     <t>Planta</t>
   </si>
@@ -3488,7 +3488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1002"/>
+  <dimension ref="A1:F1007"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.6328125" customWidth="1"/>
@@ -3526,8 +3526,8 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <f>+F282</f>
-        <v>13992</v>
+        <f>+F287</f>
+        <v>14245</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -9007,29 +9007,124 @@
       </c>
     </row>
     <row r="282" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A282" s="5"/>
-      <c r="B282" s="5"/>
-      <c r="C282" s="5"/>
-      <c r="D282" s="5"/>
-      <c r="E282" s="5"/>
-      <c r="F282" s="5">
-        <f>SUBTOTAL(109,(F10:F281))</f>
-        <v>13992</v>
+      <c r="A282" s="4">
+        <v>46183</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C282" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D282" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E282" s="5">
+        <v>1628</v>
+      </c>
+      <c r="F282" s="13">
+        <v>50</v>
       </c>
     </row>
     <row r="283" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A283" s="5"/>
-      <c r="B283" s="5"/>
-      <c r="C283" s="5"/>
-      <c r="D283" s="5"/>
-      <c r="E283" s="5"/>
-      <c r="F283" s="5"/>
-    </row>
-    <row r="284" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="285" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="286" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="287" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="288" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="A283" s="4">
+        <v>46188</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C283" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D283" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E283" s="5">
+        <v>1629</v>
+      </c>
+      <c r="F283" s="13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A284" s="4">
+        <v>46192</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C284" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D284" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E284" s="5">
+        <v>1630</v>
+      </c>
+      <c r="F284" s="13">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A285" s="4">
+        <v>46197</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C285" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D285" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E285" s="5">
+        <v>1631</v>
+      </c>
+      <c r="F285" s="13">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A286" s="4">
+        <v>46199</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C286" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D286" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E286" s="5">
+        <v>1632</v>
+      </c>
+      <c r="F286" s="13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A287" s="5"/>
+      <c r="B287" s="5"/>
+      <c r="C287" s="5"/>
+      <c r="D287" s="5"/>
+      <c r="E287" s="5"/>
+      <c r="F287" s="5">
+        <f>SUBTOTAL(109,(F10:F286))</f>
+        <v>14245</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A288" s="5"/>
+      <c r="B288" s="5"/>
+      <c r="C288" s="5"/>
+      <c r="D288" s="5"/>
+      <c r="E288" s="5"/>
+      <c r="F288" s="5"/>
+    </row>
     <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -9744,6 +9839,11 @@
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1001" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1002" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1003" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1004" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1005" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1006" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1007" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="A9:F281" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">

--- a/DIESEL SERFOCOL- V01.xlsx
+++ b/DIESEL SERFOCOL- V01.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\STREAMLIT WEB\SERFOCOL PROGRAMACION PY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC184282-B31A-40F1-8532-836115384B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34484879-6BAB-4ABC-A066-10B2587D79B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="39">
   <si>
     <t>Planta</t>
   </si>
@@ -200,11 +200,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -411,15 +418,15 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -431,11 +438,11 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -450,49 +457,52 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3488,7 +3498,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1007"/>
+  <dimension ref="A1:F1014"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.6328125" customWidth="1"/>
@@ -3501,20 +3511,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="26"/>
-      <c r="B1" s="26"/>
+      <c r="A1" s="27"/>
+      <c r="B1" s="27"/>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
     </row>
     <row r="3" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
+      <c r="A3" s="27"/>
+      <c r="B3" s="27"/>
     </row>
     <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26"/>
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
     </row>
     <row r="5" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
@@ -3526,8 +3536,8 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <f>+F287</f>
-        <v>14245</v>
+        <f>+F294</f>
+        <v>14592</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -9107,40 +9117,173 @@
       </c>
     </row>
     <row r="287" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A287" s="5"/>
-      <c r="B287" s="5"/>
-      <c r="C287" s="5"/>
-      <c r="D287" s="5"/>
-      <c r="E287" s="5"/>
-      <c r="F287" s="5">
-        <f>SUBTOTAL(109,(F10:F286))</f>
-        <v>14245</v>
+      <c r="A287" s="26">
+        <v>46209</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C287" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D287" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E287" s="5">
+        <v>1633</v>
+      </c>
+      <c r="F287" s="13">
+        <v>50</v>
       </c>
     </row>
     <row r="288" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A288" s="5"/>
-      <c r="B288" s="5"/>
-      <c r="C288" s="5"/>
-      <c r="D288" s="5"/>
-      <c r="E288" s="5"/>
-      <c r="F288" s="5"/>
-    </row>
-    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="A288" s="26">
+        <v>46212</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C288" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D288" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E288" s="5">
+        <v>1634</v>
+      </c>
+      <c r="F288" s="13">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A289" s="26">
+        <v>46216</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C289" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D289" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E289" s="5">
+        <v>1635</v>
+      </c>
+      <c r="F289" s="13">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A290" s="26">
+        <v>46220</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C290" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D290" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E290" s="5">
+        <v>1636</v>
+      </c>
+      <c r="F290" s="13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A291" s="26">
+        <v>46225</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C291" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D291" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E291" s="5">
+        <v>1637</v>
+      </c>
+      <c r="F291" s="13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A292" s="4">
+        <v>46228</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C292" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D292" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E292" s="5">
+        <v>1639</v>
+      </c>
+      <c r="F292" s="13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A293" s="4">
+        <v>46232</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C293" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D293" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E293" s="5">
+        <v>1640</v>
+      </c>
+      <c r="F293" s="13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A294" s="5"/>
+      <c r="B294" s="5"/>
+      <c r="C294" s="5"/>
+      <c r="D294" s="5"/>
+      <c r="E294" s="5"/>
+      <c r="F294" s="5">
+        <f>SUBTOTAL(109,(F10:F293))</f>
+        <v>14592</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A295" s="5"/>
+      <c r="B295" s="5"/>
+      <c r="C295" s="5"/>
+      <c r="D295" s="5"/>
+      <c r="E295" s="5"/>
+      <c r="F295" s="5"/>
+    </row>
+    <row r="296" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="297" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="298" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="299" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="300" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="301" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="302" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="303" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="304" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -9844,6 +9987,13 @@
     <row r="1005" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1006" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1007" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1008" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1009" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1010" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1011" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1012" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1013" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1014" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="A9:F281" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
@@ -9871,40 +10021,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
     </row>
     <row r="3" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
     </row>
     <row r="4" spans="2:17" ht="26" x14ac:dyDescent="0.6">
       <c r="B4" s="17"/>
@@ -9974,10 +10124,10 @@
       <c r="B6" s="23">
         <v>2023</v>
       </c>
-      <c r="C6" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="28" t="s">
+      <c r="C6" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="29" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="20">
@@ -10025,8 +10175,8 @@
       <c r="B7" s="23">
         <v>2024</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
       <c r="E7" s="20">
         <v>380</v>
       </c>
@@ -10072,8 +10222,8 @@
       <c r="B8" s="23">
         <v>2025</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
       <c r="E8" s="20">
         <v>459.5</v>
       </c>
@@ -10119,8 +10269,8 @@
       <c r="B9" s="23">
         <v>2026</v>
       </c>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
       <c r="E9" s="20">
         <v>443</v>
       </c>

--- a/DIESEL SERFOCOL- V01.xlsx
+++ b/DIESEL SERFOCOL- V01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\STREAMLIT WEB\SERFOCOL PROGRAMACION PY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34484879-6BAB-4ABC-A066-10B2587D79B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEFF2CA-F62F-4318-81B9-EE07182D7583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DIESEL SERFOCOL" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="40">
   <si>
     <t>Planta</t>
   </si>
@@ -195,16 +195,26 @@
   <si>
     <t>Camilo Aguayo</t>
   </si>
+  <si>
+    <t>Retroexabadora</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -418,15 +428,15 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -438,11 +448,11 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -457,53 +467,56 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3498,7 +3511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1014"/>
+  <dimension ref="A1:F1015"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.6328125" customWidth="1"/>
@@ -3536,8 +3549,8 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <f>+F294</f>
-        <v>14592</v>
+        <f>+F295</f>
+        <v>14672</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -9257,14 +9270,23 @@
       </c>
     </row>
     <row r="294" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A294" s="5"/>
-      <c r="B294" s="5"/>
-      <c r="C294" s="5"/>
-      <c r="D294" s="5"/>
-      <c r="E294" s="5"/>
-      <c r="F294" s="5">
-        <f>SUBTOTAL(109,(F10:F293))</f>
-        <v>14592</v>
+      <c r="A294" s="4">
+        <v>46245</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C294" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D294" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E294" s="5">
+        <v>1641</v>
+      </c>
+      <c r="F294" s="13">
+        <v>80</v>
       </c>
     </row>
     <row r="295" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -9273,9 +9295,19 @@
       <c r="C295" s="5"/>
       <c r="D295" s="5"/>
       <c r="E295" s="5"/>
-      <c r="F295" s="5"/>
-    </row>
-    <row r="296" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="F295" s="5">
+        <f>SUBTOTAL(109,(F10:F294))</f>
+        <v>14672</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A296" s="5"/>
+      <c r="B296" s="5"/>
+      <c r="C296" s="5"/>
+      <c r="D296" s="5"/>
+      <c r="E296" s="5"/>
+      <c r="F296" s="5"/>
+    </row>
     <row r="297" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="298" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="299" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -9994,6 +10026,7 @@
     <row r="1012" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1013" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1014" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1015" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="A9:F281" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">

--- a/DIESEL SERFOCOL- V01.xlsx
+++ b/DIESEL SERFOCOL- V01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Acer\Desktop\STREAMLIT WEB\SERFOCOL PROGRAMACION PY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EEFF2CA-F62F-4318-81B9-EE07182D7583}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18748DF-0169-4DC2-BA3B-7E046E6C0496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DIESEL SERFOCOL" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="40">
   <si>
     <t>Planta</t>
   </si>
@@ -500,6 +500,9 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -514,9 +517,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3511,7 +3511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1015"/>
+  <dimension ref="A1:F1019"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.6328125" customWidth="1"/>
@@ -3524,20 +3524,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="27"/>
-      <c r="B1" s="27"/>
+      <c r="A1" s="28"/>
+      <c r="B1" s="28"/>
     </row>
     <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
     </row>
     <row r="3" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
     </row>
     <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="27"/>
-      <c r="B4" s="27"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
     </row>
     <row r="5" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
@@ -3549,8 +3549,8 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <f>+F295</f>
-        <v>14672</v>
+        <f>+F299</f>
+        <v>14864</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
@@ -9279,7 +9279,7 @@
       <c r="C294" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D294" s="32" t="s">
+      <c r="D294" s="27" t="s">
         <v>39</v>
       </c>
       <c r="E294" s="5">
@@ -9290,28 +9290,104 @@
       </c>
     </row>
     <row r="295" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A295" s="5"/>
-      <c r="B295" s="5"/>
-      <c r="C295" s="5"/>
-      <c r="D295" s="5"/>
-      <c r="E295" s="5"/>
-      <c r="F295" s="5">
-        <f>SUBTOTAL(109,(F10:F294))</f>
-        <v>14672</v>
+      <c r="A295" s="4">
+        <v>46251</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C295" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D295" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E295" s="5">
+        <v>1642</v>
+      </c>
+      <c r="F295" s="13">
+        <v>45</v>
       </c>
     </row>
     <row r="296" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A296" s="5"/>
-      <c r="B296" s="5"/>
-      <c r="C296" s="5"/>
-      <c r="D296" s="5"/>
-      <c r="E296" s="5"/>
-      <c r="F296" s="5"/>
-    </row>
-    <row r="297" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="298" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="299" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="300" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="A296" s="4">
+        <v>46254</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C296" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D296" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E296" s="5">
+        <v>1643</v>
+      </c>
+      <c r="F296" s="13">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A297" s="4">
+        <v>46258</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C297" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D297" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E297" s="5">
+        <v>1644</v>
+      </c>
+      <c r="F297" s="13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A298" s="4">
+        <v>46261</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C298" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D298" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E298" s="5">
+        <v>1645</v>
+      </c>
+      <c r="F298" s="13">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A299" s="5"/>
+      <c r="B299" s="5"/>
+      <c r="C299" s="5"/>
+      <c r="D299" s="5"/>
+      <c r="E299" s="5"/>
+      <c r="F299" s="5">
+        <f>SUBTOTAL(109,(F10:F298))</f>
+        <v>14864</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A300" s="5"/>
+      <c r="B300" s="5"/>
+      <c r="C300" s="5"/>
+      <c r="D300" s="5"/>
+      <c r="E300" s="5"/>
+      <c r="F300" s="5"/>
+    </row>
     <row r="301" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="302" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="303" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -10027,6 +10103,10 @@
     <row r="1013" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1014" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="1015" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1016" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1017" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1018" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="1019" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="A9:F281" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
@@ -10054,40 +10134,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.35">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
     </row>
     <row r="3" spans="2:17" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="29"/>
+      <c r="L3" s="29"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
     </row>
     <row r="4" spans="2:17" ht="26" x14ac:dyDescent="0.6">
       <c r="B4" s="17"/>
@@ -10157,10 +10237,10 @@
       <c r="B6" s="23">
         <v>2023</v>
       </c>
-      <c r="C6" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="29" t="s">
+      <c r="C6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="30" t="s">
         <v>6</v>
       </c>
       <c r="E6" s="20">
@@ -10208,8 +10288,8 @@
       <c r="B7" s="23">
         <v>2024</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
       <c r="E7" s="20">
         <v>380</v>
       </c>
@@ -10255,8 +10335,8 @@
       <c r="B8" s="23">
         <v>2025</v>
       </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
       <c r="E8" s="20">
         <v>459.5</v>
       </c>
@@ -10302,8 +10382,8 @@
       <c r="B9" s="23">
         <v>2026</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
       <c r="E9" s="20">
         <v>443</v>
       </c>
